--- a/practice/answers/q057.xlsx
+++ b/practice/answers/q057.xlsx
@@ -70110,21 +70110,21 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>(c) SY Manness has the higher average (72.1 vs 59.6); AAC Brandon has far more data (519 rows vs 108).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>(d) The average and the count measure different things: an average can rest on a handful of rows. Here the higher-average variety has about a fifth as many results -- the two facts are independent, which is exactly what the two counts show.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>(e) An average from a few rows can move a long way with one more result, so the count tells the reader how much weight the average can bear.</t>
